--- a/00_output/20_alternative_competition_ratios.xlsx
+++ b/00_output/20_alternative_competition_ratios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,68 +473,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>central_ac_efficient_electric_residential</t>
+          <t>fridge_efficient_electric_residential</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>central_ac_baseline_electric_residential</t>
+          <t>fridge_baseline_electric_residential</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>central_ac_existing_electric_residential</t>
+          <t>fridge_top10_electric_residential</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
-        <is>
-          <t>room_ac_efficient_electric_residential</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>room_ac_baseline_electric_residential</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>room_ac_existing_electric_residential</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>fridge_efficient_electric_residential</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>fridge_baseline_electric_residential</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>fridge_top10_electric_residential</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
         <is>
           <t>fridge_existing_electric_residential</t>
         </is>

--- a/00_output/20_alternative_competition_ratios.xlsx
+++ b/00_output/20_alternative_competition_ratios.xlsx
@@ -431,70 +431,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>furnace_efficient_oil_residential</t>
+          <t>furnace_oil_efficient_residential</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>furnace_baseline_oil_residential</t>
+          <t>furnace_oil_baseline_residential</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>furnace_existing_oil_residential</t>
+          <t>furnace_oil_existing_residential</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>furnace_efficient_natural_gas_residential</t>
+          <t>furnace_natural_gas_efficient_residential</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>furnace_baseline_natural_gas_residential</t>
+          <t>furnace_natural_gas_baseline_residential</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>furnace_existing_natural_gas_residential</t>
+          <t>furnace_natural_gas_existing_residential</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fridge_efficient_electric_residential</t>
+          <t>fridge_electric_efficient_residential</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fridge_baseline_electric_residential</t>
+          <t>fridge_electric_baseline_residential</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fridge_top10_electric_residential</t>
+          <t>fridge_electric_top10_residential</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fridge_existing_electric_residential</t>
+          <t>fridge_electric_existing_residential</t>
         </is>
       </c>
     </row>

--- a/00_output/20_alternative_competition_ratios.xlsx
+++ b/00_output/20_alternative_competition_ratios.xlsx
@@ -473,28 +473,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fridge_electric_efficient_residential</t>
+          <t>refrigerator_electric_efficient_residential</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fridge_electric_baseline_residential</t>
+          <t>refrigerator_electric_baseline_residential</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fridge_electric_top10_residential</t>
+          <t>refrigerator_electric_top10_residential</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fridge_electric_existing_residential</t>
+          <t>refrigerator_electric_existing_residential</t>
         </is>
       </c>
     </row>

--- a/00_output/20_alternative_competition_ratios.xlsx
+++ b/00_output/20_alternative_competition_ratios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,68 +431,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>furnace_oil_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>furnace_oil_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>furnace_oil_existing_residential</t>
+          <t>furnace_oil_existing_residential_1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_existing_residential</t>
+          <t>furnace_oil_existing_residential_2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>refrigerator_electric_efficient_residential</t>
+          <t>furnace_natural_gas_efficient_residential_1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>refrigerator_electric_baseline_residential</t>
+          <t>furnace_natural_gas_baseline_residential_1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>refrigerator_electric_top10_residential</t>
+          <t>furnace_natural_gas_existing_residential_1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_efficient_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_baseline_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_existing_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_efficient_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_baseline_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_top10_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>refrigerator_electric_existing_residential</t>
         </is>

--- a/00_output/20_alternative_competition_ratios.xlsx
+++ b/00_output/20_alternative_competition_ratios.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,31 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -42,12 +57,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,132 +458,153 @@
   </sheetPr>
   <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>unique_measure_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>furnace_oil_efficient_residential_1</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>furnace_oil_efficient_residential_1a</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>furnace_oil_baseline_residential_1</t>
-        </is>
-      </c>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>furnace_oil_baseline_residential_1a</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>furnace_oil_existing_residential_1</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>furnace_oil_existing_residential_1a</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>furnace_oil_efficient_residential_2</t>
-        </is>
-      </c>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>furnace_oil_efficient_residential_3b</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>furnace_oil_baseline_residential_2</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>furnace_oil_baseline_residential_3b</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>furnace_oil_existing_residential_2</t>
-        </is>
-      </c>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>furnace_oil_existing_residential_3b</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_efficient_residential_1</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_efficient_residential_1a</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_baseline_residential_1</t>
-        </is>
-      </c>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_baseline_residential_1a</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_existing_residential_1</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_existing_residential_1a</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_efficient_residential_2</t>
-        </is>
-      </c>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_efficient_residential_3b</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_baseline_residential_2</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_baseline_residential_3b</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_existing_residential_2</t>
-        </is>
-      </c>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_existing_residential_3b</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>refrigerator_electric_efficient_residential</t>
         </is>
       </c>
+      <c r="B14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>refrigerator_electric_baseline_residential</t>
         </is>
       </c>
+      <c r="B15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>refrigerator_electric_top10_residential</t>
         </is>
       </c>
+      <c r="B16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>refrigerator_electric_existing_residential</t>
         </is>
       </c>
+      <c r="B17" s="5" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/00_output/20_alternative_competition_ratios.xlsx
+++ b/00_output/20_alternative_competition_ratios.xlsx
@@ -459,8 +459,8 @@
   <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
